--- a/_106_Weapons.xlsx
+++ b/_106_Weapons.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\UnityPortfolioProjectTables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\NextHorizonTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{539D6E99-EF2A-48F2-B75A-1C878FC64084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4332D669-EABC-40E8-A154-4B8B8628C390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
   <si>
     <t>key</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -51,7 +51,23 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>tier</t>
+    <t>grade</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Legend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Epic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rare</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EGrade</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -126,13 +142,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -415,13 +431,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:E54"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="34" width="12.5703125" style="4" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="4"/>
+    <col min="1" max="34" width="12.5625" style="4" customWidth="1"/>
+    <col min="35" max="16384" width="9.125" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -438,12 +454,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
@@ -455,12 +471,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A4" s="2">
         <v>1060001</v>
       </c>
-      <c r="B4" s="2">
-        <v>1</v>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="C4" s="2">
         <v>9030001</v>
@@ -472,12 +488,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A5" s="3">
         <v>1060002</v>
       </c>
-      <c r="B5" s="3">
-        <v>1</v>
+      <c r="B5" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="C5" s="3">
         <v>9030002</v>
@@ -489,12 +505,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A6" s="2">
         <v>1060003</v>
       </c>
-      <c r="B6" s="2">
-        <v>2</v>
+      <c r="B6" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="C6" s="2">
         <v>9030003</v>
@@ -506,12 +522,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A7" s="3">
         <v>1060004</v>
       </c>
-      <c r="B7" s="3">
-        <v>2</v>
+      <c r="B7" s="3" t="s">
+        <v>7</v>
       </c>
       <c r="C7" s="3">
         <v>9030004</v>
@@ -523,53 +539,53 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="9" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="11" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="12" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="13" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="14" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="15" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="16" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="17" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="18" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="19" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="20" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="21" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="22" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="23" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="24" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="25" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="26" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="27" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="28" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="29" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="30" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="31" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="32" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="33" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="34" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="35" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="36" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="37" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="38" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="39" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="40" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="41" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="42" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="43" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="44" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="45" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="46" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="47" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="48" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="49" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="50" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="51" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="52" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="53" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="54" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="9" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="11" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="12" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="13" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="14" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="15" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="16" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="17" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="18" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="19" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="20" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="21" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="22" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="23" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="24" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="25" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="26" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="27" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="28" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="29" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="30" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="31" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="32" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="33" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="34" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="35" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="36" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="37" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="38" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="39" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="40" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="41" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="42" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="43" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="44" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="45" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="46" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="47" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="48" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="49" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="50" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="51" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="52" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="53" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="54" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_106_Weapons.xlsx
+++ b/_106_Weapons.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\NextHorizonTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4332D669-EABC-40E8-A154-4B8B8628C390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B8FF459-2411-495E-9E60-02EA3FAACCA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20550" yWindow="1760" windowWidth="21600" windowHeight="11330" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>key</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -69,6 +69,14 @@
   <si>
     <t>EGrade</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>desc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -430,14 +438,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:E54"/>
+  <dimension ref="A2:F54"/>
   <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="34" width="12.5625" style="4" customWidth="1"/>
-    <col min="35" max="16384" width="9.125" style="4"/>
+    <col min="1" max="35" width="12.5625" style="4" customWidth="1"/>
+    <col min="36" max="16384" width="9.125" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -448,13 +456,16 @@
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -465,13 +476,16 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A4" s="2">
         <v>1060001</v>
       </c>
@@ -479,16 +493,19 @@
         <v>9</v>
       </c>
       <c r="C4" s="2">
-        <v>9030001</v>
+        <v>9070001</v>
       </c>
       <c r="D4" s="2">
+        <v>9070002</v>
+      </c>
+      <c r="E4" s="2">
         <v>1010001</v>
       </c>
-      <c r="E4" s="2">
+      <c r="F4" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A5" s="3">
         <v>1060002</v>
       </c>
@@ -496,16 +513,19 @@
         <v>9</v>
       </c>
       <c r="C5" s="3">
-        <v>9030002</v>
+        <v>9070003</v>
       </c>
       <c r="D5" s="3">
+        <v>9070004</v>
+      </c>
+      <c r="E5" s="3">
         <v>1010001</v>
       </c>
-      <c r="E5" s="3">
+      <c r="F5" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A6" s="2">
         <v>1060003</v>
       </c>
@@ -513,16 +533,19 @@
         <v>8</v>
       </c>
       <c r="C6" s="2">
-        <v>9030003</v>
+        <v>9070005</v>
       </c>
       <c r="D6" s="2">
+        <v>9070006</v>
+      </c>
+      <c r="E6" s="2">
         <v>1010001</v>
       </c>
-      <c r="E6" s="2">
+      <c r="F6" s="2">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A7" s="3">
         <v>1060004</v>
       </c>
@@ -530,24 +553,27 @@
         <v>7</v>
       </c>
       <c r="C7" s="3">
-        <v>9030004</v>
+        <v>9070007</v>
       </c>
       <c r="D7" s="3">
+        <v>9070008</v>
+      </c>
+      <c r="E7" s="3">
         <v>1010001</v>
       </c>
-      <c r="E7" s="3">
+      <c r="F7" s="3">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="9" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="11" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="12" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="13" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="14" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="15" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="16" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="8" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="9" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="10" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="11" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="12" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="13" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="14" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="15" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="16" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
     <row r="17" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
     <row r="18" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
     <row r="19" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
